--- a/TestCase Template.xlsx
+++ b/TestCase Template.xlsx
@@ -1,25 +1,38 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0665e26162787795/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="122" documentId="8_{CF058D5A-DAA0-44A1-B83E-692BC6468603}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7C6F752B-59E0-4D25-9F5E-1AFBB5D5261F}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="9615"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Test Case 1" sheetId="1" r:id="rId1"/>
+    <sheet name="Template" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="70">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -257,15 +270,111 @@
   <si>
     <t>Failed</t>
   </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Ritika Ghogare</t>
+  </si>
+  <si>
+    <t>Test the functionality of windows calculator</t>
+  </si>
+  <si>
+    <t>Version:01</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Shreya Jaiswal</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Test a entire Functionality of </t>
+  </si>
+  <si>
+    <t xml:space="preserve">open calculator Application   </t>
+  </si>
+  <si>
+    <t>Verify that the Application is open</t>
+  </si>
+  <si>
+    <t>Subtraction
+a) Click 5-3=</t>
+  </si>
+  <si>
+    <t>Multiplication
+Click 5*3=</t>
+  </si>
+  <si>
+    <t>Division
+Click 5/3=</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify the Addition result is" 7" .
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify the Subtraction result is "2" .
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify the Multiplication result is "15"
+</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Verify the Division result is "1.67" .</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Addition Of Numbers
+a) Click 5 + 3=
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">For Clear Screen
+Every single operation perfrom after clear the calculator sreen Click "c" or "CE".
+</t>
+  </si>
+  <si>
+    <t>Decimal /floating point Calculation 
+Click 6.6+4.25=</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify the Decimal point result is "10.85" .
+</t>
+  </si>
+  <si>
+    <t>Verify the Claculator Screen shows 0 (zero) .</t>
+  </si>
+  <si>
+    <t>Division by zero 
+Click 6/0=</t>
+  </si>
+  <si>
+    <t>Verify the Shows this messeage "Can not divide by zero"</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mmmm\ d&quot;, &quot;yyyy"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -299,6 +408,36 @@
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="8"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -634,8 +773,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+  <cellXfs count="67">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -708,38 +847,66 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -747,17 +914,35 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -777,8 +962,97 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>765862</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>57923</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1108810</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>353239</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{40A4C715-58E6-50E0-02CE-17D6085740A8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1879257" y="2497095"/>
+          <a:ext cx="342948" cy="295316"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>128717</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>148023</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1190625</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>1428749</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Picture 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{566DF553-067B-4080-9B3C-C9809B728557}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3404545" y="2587195"/>
+          <a:ext cx="1061908" cy="1280726"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -978,7 +1252,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Y994"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
@@ -991,10 +1265,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="39" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="28"/>
+      <c r="B1" s="40"/>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1002,13 +1276,13 @@
         <v>2</v>
       </c>
       <c r="E1" s="3"/>
-      <c r="F1" s="29" t="s">
+      <c r="F1" s="59" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="31"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="47"/>
+      <c r="J1" s="48"/>
       <c r="K1" s="4"/>
       <c r="L1" s="4"/>
       <c r="M1" s="4"/>
@@ -1026,10 +1300,10 @@
       <c r="Y1" s="4"/>
     </row>
     <row r="2" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="33"/>
+      <c r="B2" s="32"/>
       <c r="C2" s="5" t="s">
         <v>5</v>
       </c>
@@ -1037,14 +1311,14 @@
         <v>6</v>
       </c>
       <c r="E2" s="7"/>
-      <c r="F2" s="34" t="s">
+      <c r="F2" s="51" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="33"/>
-      <c r="H2" s="35" t="s">
+      <c r="G2" s="32"/>
+      <c r="H2" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="33"/>
+      <c r="I2" s="32"/>
       <c r="J2" s="8" t="s">
         <v>9</v>
       </c>
@@ -1065,10 +1339,10 @@
       <c r="Y2" s="4"/>
     </row>
     <row r="3" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="32" t="s">
+      <c r="A3" s="44" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="33"/>
+      <c r="B3" s="32"/>
       <c r="C3" s="5" t="s">
         <v>11</v>
       </c>
@@ -1076,14 +1350,14 @@
         <v>12</v>
       </c>
       <c r="E3" s="7"/>
-      <c r="F3" s="36">
+      <c r="F3" s="60">
         <v>46220</v>
       </c>
-      <c r="G3" s="33"/>
-      <c r="H3" s="35" t="s">
+      <c r="G3" s="32"/>
+      <c r="H3" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="I3" s="33"/>
+      <c r="I3" s="32"/>
       <c r="J3" s="9" t="s">
         <v>14</v>
       </c>
@@ -1134,21 +1408,21 @@
       <c r="A5" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="39" t="s">
+      <c r="B5" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="37"/>
-      <c r="D5" s="33"/>
+      <c r="C5" s="31"/>
+      <c r="D5" s="32"/>
       <c r="E5" s="14"/>
       <c r="F5" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="35" t="s">
+      <c r="G5" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="H5" s="37"/>
-      <c r="I5" s="37"/>
-      <c r="J5" s="38"/>
+      <c r="H5" s="31"/>
+      <c r="I5" s="31"/>
+      <c r="J5" s="34"/>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
       <c r="M5" s="4"/>
@@ -1169,21 +1443,21 @@
       <c r="A6" s="16">
         <v>1</v>
       </c>
-      <c r="B6" s="34" t="s">
+      <c r="B6" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="37"/>
-      <c r="D6" s="33"/>
+      <c r="C6" s="31"/>
+      <c r="D6" s="32"/>
       <c r="E6" s="5"/>
       <c r="F6" s="17">
         <v>1</v>
       </c>
-      <c r="G6" s="34" t="s">
+      <c r="G6" s="51" t="s">
         <v>19</v>
       </c>
-      <c r="H6" s="37"/>
-      <c r="I6" s="37"/>
-      <c r="J6" s="38"/>
+      <c r="H6" s="31"/>
+      <c r="I6" s="31"/>
+      <c r="J6" s="34"/>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
       <c r="M6" s="4"/>
@@ -1204,21 +1478,21 @@
       <c r="A7" s="16">
         <v>2</v>
       </c>
-      <c r="B7" s="34" t="s">
+      <c r="B7" s="51" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="37"/>
-      <c r="D7" s="33"/>
+      <c r="C7" s="31"/>
+      <c r="D7" s="32"/>
       <c r="E7" s="5"/>
       <c r="F7" s="17">
         <v>2</v>
       </c>
-      <c r="G7" s="34" t="s">
+      <c r="G7" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="H7" s="37"/>
-      <c r="I7" s="37"/>
-      <c r="J7" s="38"/>
+      <c r="H7" s="31"/>
+      <c r="I7" s="31"/>
+      <c r="J7" s="34"/>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
       <c r="M7" s="4"/>
@@ -1239,17 +1513,17 @@
       <c r="A8" s="16">
         <v>3</v>
       </c>
-      <c r="B8" s="34"/>
-      <c r="C8" s="37"/>
-      <c r="D8" s="33"/>
+      <c r="B8" s="51"/>
+      <c r="C8" s="31"/>
+      <c r="D8" s="32"/>
       <c r="E8" s="5"/>
       <c r="F8" s="17">
         <v>3</v>
       </c>
-      <c r="G8" s="34"/>
-      <c r="H8" s="37"/>
-      <c r="I8" s="37"/>
-      <c r="J8" s="38"/>
+      <c r="G8" s="51"/>
+      <c r="H8" s="31"/>
+      <c r="I8" s="31"/>
+      <c r="J8" s="34"/>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
       <c r="M8" s="4"/>
@@ -1270,17 +1544,17 @@
       <c r="A9" s="18">
         <v>4</v>
       </c>
-      <c r="B9" s="40"/>
-      <c r="C9" s="41"/>
-      <c r="D9" s="42"/>
+      <c r="B9" s="52"/>
+      <c r="C9" s="53"/>
+      <c r="D9" s="54"/>
       <c r="E9" s="19"/>
       <c r="F9" s="20">
         <v>4</v>
       </c>
-      <c r="G9" s="40"/>
-      <c r="H9" s="41"/>
-      <c r="I9" s="41"/>
-      <c r="J9" s="43"/>
+      <c r="G9" s="52"/>
+      <c r="H9" s="53"/>
+      <c r="I9" s="53"/>
+      <c r="J9" s="55"/>
       <c r="K9" s="21"/>
       <c r="L9" s="4"/>
       <c r="M9" s="4"/>
@@ -1328,17 +1602,17 @@
       <c r="A11" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="B11" s="44" t="s">
+      <c r="B11" s="61" t="s">
         <v>23</v>
       </c>
-      <c r="C11" s="45"/>
-      <c r="D11" s="45"/>
-      <c r="E11" s="45"/>
-      <c r="F11" s="45"/>
-      <c r="G11" s="45"/>
-      <c r="H11" s="45"/>
-      <c r="I11" s="45"/>
-      <c r="J11" s="45"/>
+      <c r="C11" s="57"/>
+      <c r="D11" s="57"/>
+      <c r="E11" s="57"/>
+      <c r="F11" s="57"/>
+      <c r="G11" s="57"/>
+      <c r="H11" s="57"/>
+      <c r="I11" s="57"/>
+      <c r="J11" s="57"/>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
       <c r="M11" s="4"/>
@@ -1357,17 +1631,17 @@
     </row>
     <row r="12" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="4"/>
-      <c r="B12" s="46" t="s">
+      <c r="B12" s="62" t="s">
         <v>24</v>
       </c>
-      <c r="C12" s="45"/>
-      <c r="D12" s="45"/>
-      <c r="E12" s="45"/>
-      <c r="F12" s="45"/>
-      <c r="G12" s="45"/>
-      <c r="H12" s="45"/>
-      <c r="I12" s="45"/>
-      <c r="J12" s="45"/>
+      <c r="C12" s="57"/>
+      <c r="D12" s="57"/>
+      <c r="E12" s="57"/>
+      <c r="F12" s="57"/>
+      <c r="G12" s="57"/>
+      <c r="H12" s="57"/>
+      <c r="I12" s="57"/>
+      <c r="J12" s="57"/>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
       <c r="M12" s="4"/>
@@ -1415,23 +1689,23 @@
       <c r="A14" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="B14" s="47" t="s">
+      <c r="B14" s="46" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="28"/>
-      <c r="D14" s="47" t="s">
+      <c r="C14" s="40"/>
+      <c r="D14" s="46" t="s">
         <v>27</v>
       </c>
-      <c r="E14" s="28"/>
-      <c r="F14" s="47" t="s">
+      <c r="E14" s="40"/>
+      <c r="F14" s="46" t="s">
         <v>28</v>
       </c>
-      <c r="G14" s="30"/>
-      <c r="H14" s="28"/>
-      <c r="I14" s="47" t="s">
+      <c r="G14" s="47"/>
+      <c r="H14" s="40"/>
+      <c r="I14" s="46" t="s">
         <v>29</v>
       </c>
-      <c r="J14" s="31"/>
+      <c r="J14" s="48"/>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
       <c r="M14" s="4"/>
@@ -1452,23 +1726,23 @@
       <c r="A15" s="16">
         <v>1</v>
       </c>
-      <c r="B15" s="48" t="s">
+      <c r="B15" s="63" t="s">
         <v>30</v>
       </c>
-      <c r="C15" s="33"/>
-      <c r="D15" s="34" t="s">
+      <c r="C15" s="32"/>
+      <c r="D15" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="E15" s="33"/>
-      <c r="F15" s="34" t="s">
+      <c r="E15" s="32"/>
+      <c r="F15" s="51" t="s">
         <v>32</v>
       </c>
-      <c r="G15" s="37"/>
-      <c r="H15" s="33"/>
-      <c r="I15" s="34" t="s">
+      <c r="G15" s="31"/>
+      <c r="H15" s="32"/>
+      <c r="I15" s="51" t="s">
         <v>33</v>
       </c>
-      <c r="J15" s="38"/>
+      <c r="J15" s="34"/>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
       <c r="M15" s="4"/>
@@ -1489,23 +1763,23 @@
       <c r="A16" s="16">
         <v>2</v>
       </c>
-      <c r="B16" s="34" t="s">
+      <c r="B16" s="51" t="s">
         <v>34</v>
       </c>
-      <c r="C16" s="33"/>
-      <c r="D16" s="34" t="s">
+      <c r="C16" s="32"/>
+      <c r="D16" s="51" t="s">
         <v>35</v>
       </c>
-      <c r="E16" s="33"/>
-      <c r="F16" s="34" t="s">
+      <c r="E16" s="32"/>
+      <c r="F16" s="51" t="s">
         <v>32</v>
       </c>
-      <c r="G16" s="37"/>
-      <c r="H16" s="33"/>
-      <c r="I16" s="34" t="s">
+      <c r="G16" s="31"/>
+      <c r="H16" s="32"/>
+      <c r="I16" s="51" t="s">
         <v>33</v>
       </c>
-      <c r="J16" s="38"/>
+      <c r="J16" s="34"/>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
       <c r="M16" s="4"/>
@@ -1526,23 +1800,23 @@
       <c r="A17" s="16">
         <v>3</v>
       </c>
-      <c r="B17" s="34" t="s">
+      <c r="B17" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="C17" s="33"/>
-      <c r="D17" s="34" t="s">
+      <c r="C17" s="32"/>
+      <c r="D17" s="51" t="s">
         <v>37</v>
       </c>
-      <c r="E17" s="33"/>
-      <c r="F17" s="34" t="s">
+      <c r="E17" s="32"/>
+      <c r="F17" s="51" t="s">
         <v>32</v>
       </c>
-      <c r="G17" s="37"/>
-      <c r="H17" s="33"/>
-      <c r="I17" s="34" t="s">
+      <c r="G17" s="31"/>
+      <c r="H17" s="32"/>
+      <c r="I17" s="51" t="s">
         <v>33</v>
       </c>
-      <c r="J17" s="38"/>
+      <c r="J17" s="34"/>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
       <c r="M17" s="4"/>
@@ -1563,23 +1837,23 @@
       <c r="A18" s="16">
         <v>4</v>
       </c>
-      <c r="B18" s="34" t="s">
+      <c r="B18" s="51" t="s">
         <v>38</v>
       </c>
-      <c r="C18" s="33"/>
-      <c r="D18" s="34" t="s">
+      <c r="C18" s="32"/>
+      <c r="D18" s="51" t="s">
         <v>39</v>
       </c>
-      <c r="E18" s="33"/>
-      <c r="F18" s="34" t="s">
+      <c r="E18" s="32"/>
+      <c r="F18" s="51" t="s">
         <v>32</v>
       </c>
-      <c r="G18" s="37"/>
-      <c r="H18" s="33"/>
-      <c r="I18" s="34" t="s">
+      <c r="G18" s="31"/>
+      <c r="H18" s="32"/>
+      <c r="I18" s="51" t="s">
         <v>33</v>
       </c>
-      <c r="J18" s="38"/>
+      <c r="J18" s="34"/>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
       <c r="M18" s="4"/>
@@ -1597,26 +1871,26 @@
       <c r="Y18" s="4"/>
     </row>
     <row r="19" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A19" s="25">
+      <c r="A19" s="16">
         <v>5</v>
       </c>
-      <c r="B19" s="34" t="s">
+      <c r="B19" s="51" t="s">
         <v>40</v>
       </c>
-      <c r="C19" s="33"/>
-      <c r="D19" s="34" t="s">
+      <c r="C19" s="32"/>
+      <c r="D19" s="51" t="s">
         <v>35</v>
       </c>
-      <c r="E19" s="33"/>
-      <c r="F19" s="34" t="s">
+      <c r="E19" s="32"/>
+      <c r="F19" s="51" t="s">
         <v>32</v>
       </c>
-      <c r="G19" s="37"/>
-      <c r="H19" s="33"/>
-      <c r="I19" s="34" t="s">
+      <c r="G19" s="31"/>
+      <c r="H19" s="32"/>
+      <c r="I19" s="51" t="s">
         <v>33</v>
       </c>
-      <c r="J19" s="38"/>
+      <c r="J19" s="34"/>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
       <c r="M19" s="4"/>
@@ -1634,26 +1908,26 @@
       <c r="Y19" s="4"/>
     </row>
     <row r="20" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A20" s="25">
+      <c r="A20" s="16">
         <v>6</v>
       </c>
-      <c r="B20" s="34" t="s">
+      <c r="B20" s="51" t="s">
         <v>41</v>
       </c>
-      <c r="C20" s="33"/>
-      <c r="D20" s="34" t="s">
+      <c r="C20" s="32"/>
+      <c r="D20" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="E20" s="33"/>
-      <c r="F20" s="34" t="s">
+      <c r="E20" s="32"/>
+      <c r="F20" s="51" t="s">
         <v>32</v>
       </c>
-      <c r="G20" s="37"/>
-      <c r="H20" s="33"/>
-      <c r="I20" s="34" t="s">
+      <c r="G20" s="31"/>
+      <c r="H20" s="32"/>
+      <c r="I20" s="51" t="s">
         <v>33</v>
       </c>
-      <c r="J20" s="38"/>
+      <c r="J20" s="34"/>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
       <c r="M20" s="4"/>
@@ -1671,26 +1945,26 @@
       <c r="Y20" s="4"/>
     </row>
     <row r="21" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A21" s="25">
+      <c r="A21" s="16">
         <v>7</v>
       </c>
-      <c r="B21" s="34" t="s">
+      <c r="B21" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="C21" s="33"/>
-      <c r="D21" s="34" t="s">
+      <c r="C21" s="32"/>
+      <c r="D21" s="51" t="s">
         <v>35</v>
       </c>
-      <c r="E21" s="33"/>
-      <c r="F21" s="34" t="s">
+      <c r="E21" s="32"/>
+      <c r="F21" s="51" t="s">
         <v>32</v>
       </c>
-      <c r="G21" s="37"/>
-      <c r="H21" s="33"/>
-      <c r="I21" s="34" t="s">
+      <c r="G21" s="31"/>
+      <c r="H21" s="32"/>
+      <c r="I21" s="51" t="s">
         <v>33</v>
       </c>
-      <c r="J21" s="38"/>
+      <c r="J21" s="34"/>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
       <c r="M21" s="4"/>
@@ -1708,26 +1982,26 @@
       <c r="Y21" s="4"/>
     </row>
     <row r="22" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A22" s="25">
+      <c r="A22" s="16">
         <v>8</v>
       </c>
-      <c r="B22" s="34" t="s">
+      <c r="B22" s="51" t="s">
         <v>44</v>
       </c>
-      <c r="C22" s="33"/>
-      <c r="D22" s="34" t="s">
+      <c r="C22" s="32"/>
+      <c r="D22" s="51" t="s">
         <v>45</v>
       </c>
-      <c r="E22" s="33"/>
-      <c r="F22" s="34" t="s">
+      <c r="E22" s="32"/>
+      <c r="F22" s="51" t="s">
         <v>46</v>
       </c>
-      <c r="G22" s="37"/>
-      <c r="H22" s="33"/>
-      <c r="I22" s="34" t="s">
+      <c r="G22" s="31"/>
+      <c r="H22" s="32"/>
+      <c r="I22" s="51" t="s">
         <v>47</v>
       </c>
-      <c r="J22" s="38"/>
+      <c r="J22" s="34"/>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
       <c r="M22" s="4"/>
@@ -1745,18 +2019,18 @@
       <c r="Y22" s="4"/>
     </row>
     <row r="23" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="25">
+      <c r="A23" s="16">
         <v>9</v>
       </c>
-      <c r="B23" s="34"/>
-      <c r="C23" s="33"/>
-      <c r="D23" s="34"/>
-      <c r="E23" s="33"/>
-      <c r="F23" s="34"/>
-      <c r="G23" s="37"/>
-      <c r="H23" s="33"/>
-      <c r="I23" s="34"/>
-      <c r="J23" s="38"/>
+      <c r="B23" s="51"/>
+      <c r="C23" s="32"/>
+      <c r="D23" s="51"/>
+      <c r="E23" s="32"/>
+      <c r="F23" s="51"/>
+      <c r="G23" s="31"/>
+      <c r="H23" s="32"/>
+      <c r="I23" s="51"/>
+      <c r="J23" s="34"/>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
       <c r="M23" s="4"/>
@@ -1774,18 +2048,18 @@
       <c r="Y23" s="4"/>
     </row>
     <row r="24" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="25">
+      <c r="A24" s="16">
         <v>10</v>
       </c>
-      <c r="B24" s="34"/>
-      <c r="C24" s="33"/>
-      <c r="D24" s="34"/>
-      <c r="E24" s="33"/>
-      <c r="F24" s="34"/>
-      <c r="G24" s="37"/>
-      <c r="H24" s="33"/>
-      <c r="I24" s="34"/>
-      <c r="J24" s="38"/>
+      <c r="B24" s="51"/>
+      <c r="C24" s="32"/>
+      <c r="D24" s="51"/>
+      <c r="E24" s="32"/>
+      <c r="F24" s="51"/>
+      <c r="G24" s="31"/>
+      <c r="H24" s="32"/>
+      <c r="I24" s="51"/>
+      <c r="J24" s="34"/>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
       <c r="M24" s="4"/>
@@ -1803,18 +2077,18 @@
       <c r="Y24" s="4"/>
     </row>
     <row r="25" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="25">
+      <c r="A25" s="16">
         <v>11</v>
       </c>
-      <c r="B25" s="34"/>
-      <c r="C25" s="33"/>
-      <c r="D25" s="34"/>
-      <c r="E25" s="33"/>
-      <c r="F25" s="34"/>
-      <c r="G25" s="37"/>
-      <c r="H25" s="33"/>
-      <c r="I25" s="34"/>
-      <c r="J25" s="38"/>
+      <c r="B25" s="51"/>
+      <c r="C25" s="32"/>
+      <c r="D25" s="51"/>
+      <c r="E25" s="32"/>
+      <c r="F25" s="51"/>
+      <c r="G25" s="31"/>
+      <c r="H25" s="32"/>
+      <c r="I25" s="51"/>
+      <c r="J25" s="34"/>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
       <c r="M25" s="4"/>
@@ -1832,18 +2106,18 @@
       <c r="Y25" s="4"/>
     </row>
     <row r="26" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="25">
+      <c r="A26" s="16">
         <v>12</v>
       </c>
-      <c r="B26" s="34"/>
-      <c r="C26" s="33"/>
-      <c r="D26" s="34"/>
-      <c r="E26" s="33"/>
-      <c r="F26" s="34"/>
-      <c r="G26" s="37"/>
-      <c r="H26" s="33"/>
-      <c r="I26" s="34"/>
-      <c r="J26" s="38"/>
+      <c r="B26" s="51"/>
+      <c r="C26" s="32"/>
+      <c r="D26" s="51"/>
+      <c r="E26" s="32"/>
+      <c r="F26" s="51"/>
+      <c r="G26" s="31"/>
+      <c r="H26" s="32"/>
+      <c r="I26" s="51"/>
+      <c r="J26" s="34"/>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
       <c r="M26" s="4"/>
@@ -1861,18 +2135,18 @@
       <c r="Y26" s="4"/>
     </row>
     <row r="27" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="25">
+      <c r="A27" s="16">
         <v>13</v>
       </c>
-      <c r="B27" s="34"/>
-      <c r="C27" s="33"/>
-      <c r="D27" s="34"/>
-      <c r="E27" s="33"/>
-      <c r="F27" s="34"/>
-      <c r="G27" s="37"/>
-      <c r="H27" s="33"/>
-      <c r="I27" s="34"/>
-      <c r="J27" s="38"/>
+      <c r="B27" s="51"/>
+      <c r="C27" s="32"/>
+      <c r="D27" s="51"/>
+      <c r="E27" s="32"/>
+      <c r="F27" s="51"/>
+      <c r="G27" s="31"/>
+      <c r="H27" s="32"/>
+      <c r="I27" s="51"/>
+      <c r="J27" s="34"/>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
       <c r="M27" s="4"/>
@@ -1890,18 +2164,18 @@
       <c r="Y27" s="4"/>
     </row>
     <row r="28" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="25">
+      <c r="A28" s="16">
         <v>14</v>
       </c>
-      <c r="B28" s="34"/>
-      <c r="C28" s="33"/>
-      <c r="D28" s="34"/>
-      <c r="E28" s="33"/>
-      <c r="F28" s="34"/>
-      <c r="G28" s="37"/>
-      <c r="H28" s="33"/>
-      <c r="I28" s="34"/>
-      <c r="J28" s="38"/>
+      <c r="B28" s="51"/>
+      <c r="C28" s="32"/>
+      <c r="D28" s="51"/>
+      <c r="E28" s="32"/>
+      <c r="F28" s="51"/>
+      <c r="G28" s="31"/>
+      <c r="H28" s="32"/>
+      <c r="I28" s="51"/>
+      <c r="J28" s="34"/>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
       <c r="M28" s="4"/>
@@ -1919,18 +2193,18 @@
       <c r="Y28" s="4"/>
     </row>
     <row r="29" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="25">
+      <c r="A29" s="16">
         <v>15</v>
       </c>
-      <c r="B29" s="34"/>
-      <c r="C29" s="33"/>
-      <c r="D29" s="34"/>
-      <c r="E29" s="33"/>
-      <c r="F29" s="34"/>
-      <c r="G29" s="37"/>
-      <c r="H29" s="33"/>
-      <c r="I29" s="34"/>
-      <c r="J29" s="38"/>
+      <c r="B29" s="51"/>
+      <c r="C29" s="32"/>
+      <c r="D29" s="51"/>
+      <c r="E29" s="32"/>
+      <c r="F29" s="51"/>
+      <c r="G29" s="31"/>
+      <c r="H29" s="32"/>
+      <c r="I29" s="51"/>
+      <c r="J29" s="34"/>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
       <c r="M29" s="4"/>
@@ -1948,18 +2222,18 @@
       <c r="Y29" s="4"/>
     </row>
     <row r="30" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="25">
+      <c r="A30" s="16">
         <v>16</v>
       </c>
-      <c r="B30" s="34"/>
-      <c r="C30" s="33"/>
-      <c r="D30" s="34"/>
-      <c r="E30" s="33"/>
-      <c r="F30" s="34"/>
-      <c r="G30" s="37"/>
-      <c r="H30" s="33"/>
-      <c r="I30" s="34"/>
-      <c r="J30" s="38"/>
+      <c r="B30" s="51"/>
+      <c r="C30" s="32"/>
+      <c r="D30" s="51"/>
+      <c r="E30" s="32"/>
+      <c r="F30" s="51"/>
+      <c r="G30" s="31"/>
+      <c r="H30" s="32"/>
+      <c r="I30" s="51"/>
+      <c r="J30" s="34"/>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
       <c r="M30" s="4"/>
@@ -1977,18 +2251,18 @@
       <c r="Y30" s="4"/>
     </row>
     <row r="31" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="25">
+      <c r="A31" s="16">
         <v>17</v>
       </c>
-      <c r="B31" s="34"/>
-      <c r="C31" s="33"/>
-      <c r="D31" s="34"/>
-      <c r="E31" s="33"/>
-      <c r="F31" s="34"/>
-      <c r="G31" s="37"/>
-      <c r="H31" s="33"/>
-      <c r="I31" s="34"/>
-      <c r="J31" s="38"/>
+      <c r="B31" s="51"/>
+      <c r="C31" s="32"/>
+      <c r="D31" s="51"/>
+      <c r="E31" s="32"/>
+      <c r="F31" s="51"/>
+      <c r="G31" s="31"/>
+      <c r="H31" s="32"/>
+      <c r="I31" s="51"/>
+      <c r="J31" s="34"/>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
       <c r="M31" s="4"/>
@@ -2006,18 +2280,18 @@
       <c r="Y31" s="4"/>
     </row>
     <row r="32" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="25">
+      <c r="A32" s="16">
         <v>18</v>
       </c>
-      <c r="B32" s="34"/>
-      <c r="C32" s="33"/>
-      <c r="D32" s="34"/>
-      <c r="E32" s="33"/>
-      <c r="F32" s="34"/>
-      <c r="G32" s="37"/>
-      <c r="H32" s="33"/>
-      <c r="I32" s="34"/>
-      <c r="J32" s="38"/>
+      <c r="B32" s="51"/>
+      <c r="C32" s="32"/>
+      <c r="D32" s="51"/>
+      <c r="E32" s="32"/>
+      <c r="F32" s="51"/>
+      <c r="G32" s="31"/>
+      <c r="H32" s="32"/>
+      <c r="I32" s="51"/>
+      <c r="J32" s="34"/>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
       <c r="M32" s="4"/>
@@ -2035,18 +2309,18 @@
       <c r="Y32" s="4"/>
     </row>
     <row r="33" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="25">
+      <c r="A33" s="16">
         <v>19</v>
       </c>
-      <c r="B33" s="34"/>
-      <c r="C33" s="33"/>
-      <c r="D33" s="34"/>
-      <c r="E33" s="33"/>
-      <c r="F33" s="34"/>
-      <c r="G33" s="37"/>
-      <c r="H33" s="33"/>
-      <c r="I33" s="34"/>
-      <c r="J33" s="38"/>
+      <c r="B33" s="51"/>
+      <c r="C33" s="32"/>
+      <c r="D33" s="51"/>
+      <c r="E33" s="32"/>
+      <c r="F33" s="51"/>
+      <c r="G33" s="31"/>
+      <c r="H33" s="32"/>
+      <c r="I33" s="51"/>
+      <c r="J33" s="34"/>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
       <c r="M33" s="4"/>
@@ -2064,18 +2338,18 @@
       <c r="Y33" s="4"/>
     </row>
     <row r="34" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="26">
+      <c r="A34" s="18">
         <v>20</v>
       </c>
-      <c r="B34" s="40"/>
-      <c r="C34" s="42"/>
-      <c r="D34" s="40"/>
-      <c r="E34" s="42"/>
-      <c r="F34" s="40"/>
-      <c r="G34" s="41"/>
-      <c r="H34" s="42"/>
-      <c r="I34" s="40"/>
-      <c r="J34" s="43"/>
+      <c r="B34" s="52"/>
+      <c r="C34" s="54"/>
+      <c r="D34" s="52"/>
+      <c r="E34" s="54"/>
+      <c r="F34" s="52"/>
+      <c r="G34" s="53"/>
+      <c r="H34" s="54"/>
+      <c r="I34" s="52"/>
+      <c r="J34" s="55"/>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
       <c r="M34" s="4"/>
@@ -28030,6 +28304,14 @@
     <mergeCell ref="I33:J33"/>
     <mergeCell ref="B34:C34"/>
     <mergeCell ref="I34:J34"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="I31:J31"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="D17:E17"/>
     <mergeCell ref="F17:H17"/>
@@ -28042,14 +28324,6 @@
     <mergeCell ref="D19:E19"/>
     <mergeCell ref="F19:H19"/>
     <mergeCell ref="I19:J19"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="F30:H30"/>
-    <mergeCell ref="I30:J30"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="F31:H31"/>
-    <mergeCell ref="I31:J31"/>
     <mergeCell ref="B32:C32"/>
     <mergeCell ref="D32:E32"/>
     <mergeCell ref="B27:C27"/>
@@ -28120,9 +28394,777 @@
     <mergeCell ref="B8:D8"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="B15" r:id="rId1"/>
+    <hyperlink ref="B15" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <pageMargins left="1" right="1" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="landscape"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:J43"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.42578125" customWidth="1"/>
+    <col min="4" max="4" width="21.140625" customWidth="1"/>
+    <col min="5" max="5" width="3.140625" customWidth="1"/>
+    <col min="9" max="9" width="15" customWidth="1"/>
+    <col min="10" max="10" width="13.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1" s="39" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="40"/>
+      <c r="C1" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="3"/>
+      <c r="F1" s="41" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="43"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2" s="44" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="32"/>
+      <c r="C2" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="7"/>
+      <c r="F2" s="38" t="s">
+        <v>52</v>
+      </c>
+      <c r="G2" s="32"/>
+      <c r="H2" s="33" t="s">
+        <v>51</v>
+      </c>
+      <c r="I2" s="32"/>
+      <c r="J2" s="26" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A3" s="44" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="32"/>
+      <c r="C3" s="25" t="s">
+        <v>48</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="7"/>
+      <c r="F3" s="45" t="s">
+        <v>48</v>
+      </c>
+      <c r="G3" s="32"/>
+      <c r="H3" s="33" t="s">
+        <v>13</v>
+      </c>
+      <c r="I3" s="32"/>
+      <c r="J3" s="27" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A4" s="10"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
+      <c r="J4" s="12"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A5" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="31"/>
+      <c r="D5" s="32"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="H5" s="31"/>
+      <c r="I5" s="31"/>
+      <c r="J5" s="34"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A6" s="16">
+        <v>1</v>
+      </c>
+      <c r="B6" s="35"/>
+      <c r="C6" s="36"/>
+      <c r="D6" s="37"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="17">
+        <v>1</v>
+      </c>
+      <c r="G6" s="38" t="s">
+        <v>48</v>
+      </c>
+      <c r="H6" s="31"/>
+      <c r="I6" s="31"/>
+      <c r="J6" s="34"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A7" s="16">
+        <v>2</v>
+      </c>
+      <c r="B7" s="35"/>
+      <c r="C7" s="36"/>
+      <c r="D7" s="37"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="17">
+        <v>2</v>
+      </c>
+      <c r="G7" s="38" t="s">
+        <v>48</v>
+      </c>
+      <c r="H7" s="31"/>
+      <c r="I7" s="31"/>
+      <c r="J7" s="34"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A8" s="16">
+        <v>3</v>
+      </c>
+      <c r="B8" s="51"/>
+      <c r="C8" s="31"/>
+      <c r="D8" s="32"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="17">
+        <v>3</v>
+      </c>
+      <c r="G8" s="51"/>
+      <c r="H8" s="31"/>
+      <c r="I8" s="31"/>
+      <c r="J8" s="34"/>
+    </row>
+    <row r="9" spans="1:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="18">
+        <v>4</v>
+      </c>
+      <c r="B9" s="52"/>
+      <c r="C9" s="53"/>
+      <c r="D9" s="54"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="20">
+        <v>4</v>
+      </c>
+      <c r="G9" s="52"/>
+      <c r="H9" s="53"/>
+      <c r="I9" s="53"/>
+      <c r="J9" s="55"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A10" s="22"/>
+      <c r="B10" s="22"/>
+      <c r="C10" s="22"/>
+      <c r="D10" s="22"/>
+      <c r="E10" s="22"/>
+      <c r="F10" s="22"/>
+      <c r="G10" s="22"/>
+      <c r="H10" s="22"/>
+      <c r="I10" s="22"/>
+      <c r="J10" s="22"/>
+    </row>
+    <row r="11" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A11" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="56" t="s">
+        <v>53</v>
+      </c>
+      <c r="C11" s="57"/>
+      <c r="D11" s="57"/>
+      <c r="E11" s="57"/>
+      <c r="F11" s="57"/>
+      <c r="G11" s="57"/>
+      <c r="H11" s="57"/>
+      <c r="I11" s="57"/>
+      <c r="J11" s="57"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A12" s="4"/>
+      <c r="B12" s="58" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" s="57"/>
+      <c r="D12" s="57"/>
+      <c r="E12" s="57"/>
+      <c r="F12" s="57"/>
+      <c r="G12" s="57"/>
+      <c r="H12" s="57"/>
+      <c r="I12" s="57"/>
+      <c r="J12" s="57"/>
+    </row>
+    <row r="13" spans="1:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="4"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A14" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" s="46" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" s="40"/>
+      <c r="D14" s="46" t="s">
+        <v>27</v>
+      </c>
+      <c r="E14" s="40"/>
+      <c r="F14" s="46" t="s">
+        <v>28</v>
+      </c>
+      <c r="G14" s="47"/>
+      <c r="H14" s="40"/>
+      <c r="I14" s="46" t="s">
+        <v>29</v>
+      </c>
+      <c r="J14" s="48"/>
+    </row>
+    <row r="15" spans="1:10" ht="116.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="16">
+        <v>1</v>
+      </c>
+      <c r="B15" s="49" t="s">
+        <v>54</v>
+      </c>
+      <c r="C15" s="32"/>
+      <c r="D15" s="50" t="s">
+        <v>55</v>
+      </c>
+      <c r="E15" s="32"/>
+      <c r="F15" s="51"/>
+      <c r="G15" s="31"/>
+      <c r="H15" s="32"/>
+      <c r="I15" s="51"/>
+      <c r="J15" s="34"/>
+    </row>
+    <row r="16" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="16">
+        <v>2</v>
+      </c>
+      <c r="B16" s="35" t="s">
+        <v>63</v>
+      </c>
+      <c r="C16" s="37"/>
+      <c r="D16" s="50" t="s">
+        <v>59</v>
+      </c>
+      <c r="E16" s="32"/>
+      <c r="F16" s="51"/>
+      <c r="G16" s="31"/>
+      <c r="H16" s="32"/>
+      <c r="I16" s="51"/>
+      <c r="J16" s="34"/>
+    </row>
+    <row r="17" spans="1:10" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="16">
+        <v>3</v>
+      </c>
+      <c r="B17" s="35" t="s">
+        <v>64</v>
+      </c>
+      <c r="C17" s="32"/>
+      <c r="D17" s="50" t="s">
+        <v>67</v>
+      </c>
+      <c r="E17" s="32"/>
+      <c r="F17" s="51"/>
+      <c r="G17" s="31"/>
+      <c r="H17" s="32"/>
+      <c r="I17" s="51"/>
+      <c r="J17" s="34"/>
+    </row>
+    <row r="18" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="16">
+        <v>4</v>
+      </c>
+      <c r="B18" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="C18" s="32"/>
+      <c r="D18" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="E18" s="32"/>
+      <c r="F18" s="51"/>
+      <c r="G18" s="31"/>
+      <c r="H18" s="32"/>
+      <c r="I18" s="51"/>
+      <c r="J18" s="34"/>
+    </row>
+    <row r="19" spans="1:10" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="16">
+        <v>5</v>
+      </c>
+      <c r="B19" s="35" t="s">
+        <v>57</v>
+      </c>
+      <c r="C19" s="65"/>
+      <c r="D19" s="50" t="s">
+        <v>61</v>
+      </c>
+      <c r="E19" s="66"/>
+      <c r="F19" s="51"/>
+      <c r="G19" s="31"/>
+      <c r="H19" s="32"/>
+      <c r="I19" s="51"/>
+      <c r="J19" s="34"/>
+    </row>
+    <row r="20" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="16">
+        <v>6</v>
+      </c>
+      <c r="B20" s="35" t="s">
+        <v>58</v>
+      </c>
+      <c r="C20" s="65"/>
+      <c r="D20" s="38" t="s">
+        <v>62</v>
+      </c>
+      <c r="E20" s="64"/>
+      <c r="F20" s="51"/>
+      <c r="G20" s="31"/>
+      <c r="H20" s="32"/>
+      <c r="I20" s="51"/>
+      <c r="J20" s="34"/>
+    </row>
+    <row r="21" spans="1:10" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="16">
+        <v>7</v>
+      </c>
+      <c r="B21" s="35" t="s">
+        <v>65</v>
+      </c>
+      <c r="C21" s="32"/>
+      <c r="D21" s="50" t="s">
+        <v>66</v>
+      </c>
+      <c r="E21" s="32"/>
+      <c r="F21" s="51"/>
+      <c r="G21" s="31"/>
+      <c r="H21" s="32"/>
+      <c r="I21" s="51"/>
+      <c r="J21" s="34"/>
+    </row>
+    <row r="22" spans="1:10" ht="57.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="16">
+        <v>8</v>
+      </c>
+      <c r="B22" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="C22" s="32"/>
+      <c r="D22" s="50" t="s">
+        <v>69</v>
+      </c>
+      <c r="E22" s="32"/>
+      <c r="F22" s="51"/>
+      <c r="G22" s="31"/>
+      <c r="H22" s="32"/>
+      <c r="I22" s="51"/>
+      <c r="J22" s="34"/>
+    </row>
+    <row r="23" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="16">
+        <v>9</v>
+      </c>
+      <c r="B23" s="35"/>
+      <c r="C23" s="65"/>
+      <c r="D23" s="50"/>
+      <c r="E23" s="66"/>
+      <c r="F23" s="51"/>
+      <c r="G23" s="31"/>
+      <c r="H23" s="32"/>
+      <c r="I23" s="51"/>
+      <c r="J23" s="34"/>
+    </row>
+    <row r="24" spans="1:10" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="16"/>
+      <c r="B24" s="35"/>
+      <c r="C24" s="65"/>
+      <c r="D24" s="38"/>
+      <c r="E24" s="64"/>
+      <c r="F24" s="51"/>
+      <c r="G24" s="31"/>
+      <c r="H24" s="32"/>
+      <c r="I24" s="51"/>
+      <c r="J24" s="34"/>
+    </row>
+    <row r="25" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="16"/>
+      <c r="B25" s="50"/>
+      <c r="C25" s="32"/>
+      <c r="D25" s="50"/>
+      <c r="E25" s="32"/>
+      <c r="F25" s="51"/>
+      <c r="G25" s="31"/>
+      <c r="H25" s="32"/>
+      <c r="I25" s="51"/>
+      <c r="J25" s="34"/>
+    </row>
+    <row r="26" spans="1:10" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="16"/>
+      <c r="B26" s="51"/>
+      <c r="C26" s="32"/>
+      <c r="D26" s="51"/>
+      <c r="E26" s="32"/>
+      <c r="F26" s="51"/>
+      <c r="G26" s="31"/>
+      <c r="H26" s="32"/>
+      <c r="I26" s="51"/>
+      <c r="J26" s="34"/>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A27" s="16"/>
+      <c r="B27" s="51"/>
+      <c r="C27" s="32"/>
+      <c r="D27" s="51"/>
+      <c r="E27" s="32"/>
+      <c r="F27" s="51"/>
+      <c r="G27" s="31"/>
+      <c r="H27" s="32"/>
+      <c r="I27" s="51"/>
+      <c r="J27" s="34"/>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A28" s="16"/>
+      <c r="B28" s="51"/>
+      <c r="C28" s="32"/>
+      <c r="D28" s="51"/>
+      <c r="E28" s="32"/>
+      <c r="F28" s="51"/>
+      <c r="G28" s="31"/>
+      <c r="H28" s="32"/>
+      <c r="I28" s="51"/>
+      <c r="J28" s="34"/>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A29" s="16"/>
+      <c r="B29" s="51"/>
+      <c r="C29" s="32"/>
+      <c r="D29" s="51"/>
+      <c r="E29" s="32"/>
+      <c r="F29" s="51"/>
+      <c r="G29" s="31"/>
+      <c r="H29" s="32"/>
+      <c r="I29" s="51"/>
+      <c r="J29" s="34"/>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A30" s="16"/>
+      <c r="B30" s="51"/>
+      <c r="C30" s="32"/>
+      <c r="D30" s="51"/>
+      <c r="E30" s="32"/>
+      <c r="F30" s="51"/>
+      <c r="G30" s="31"/>
+      <c r="H30" s="32"/>
+      <c r="I30" s="51"/>
+      <c r="J30" s="34"/>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A31" s="16"/>
+      <c r="B31" s="51"/>
+      <c r="C31" s="32"/>
+      <c r="D31" s="51"/>
+      <c r="E31" s="32"/>
+      <c r="F31" s="51"/>
+      <c r="G31" s="31"/>
+      <c r="H31" s="32"/>
+      <c r="I31" s="51"/>
+      <c r="J31" s="34"/>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A32" s="16"/>
+      <c r="B32" s="51"/>
+      <c r="C32" s="32"/>
+      <c r="D32" s="51"/>
+      <c r="E32" s="32"/>
+      <c r="F32" s="51"/>
+      <c r="G32" s="31"/>
+      <c r="H32" s="32"/>
+      <c r="I32" s="51"/>
+      <c r="J32" s="34"/>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A33" s="16"/>
+      <c r="B33" s="51"/>
+      <c r="C33" s="32"/>
+      <c r="D33" s="51"/>
+      <c r="E33" s="32"/>
+      <c r="F33" s="51"/>
+      <c r="G33" s="31"/>
+      <c r="H33" s="32"/>
+      <c r="I33" s="51"/>
+      <c r="J33" s="34"/>
+    </row>
+    <row r="34" spans="1:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="18"/>
+      <c r="B34" s="52"/>
+      <c r="C34" s="54"/>
+      <c r="D34" s="52"/>
+      <c r="E34" s="54"/>
+      <c r="F34" s="52"/>
+      <c r="G34" s="53"/>
+      <c r="H34" s="54"/>
+      <c r="I34" s="52"/>
+      <c r="J34" s="55"/>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A35" s="4"/>
+      <c r="B35" s="4"/>
+      <c r="C35" s="4"/>
+      <c r="D35" s="4"/>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4"/>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4"/>
+      <c r="I35" s="4"/>
+      <c r="J35" s="4"/>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A36" s="4"/>
+      <c r="B36" s="4"/>
+      <c r="C36" s="4"/>
+      <c r="D36" s="4"/>
+      <c r="E36" s="4"/>
+      <c r="F36" s="4"/>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4"/>
+      <c r="I36" s="4"/>
+      <c r="J36" s="4"/>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A37" s="4"/>
+      <c r="B37" s="4"/>
+      <c r="C37" s="4"/>
+      <c r="D37" s="4"/>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4"/>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4"/>
+      <c r="I37" s="4"/>
+      <c r="J37" s="4"/>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A38" s="4"/>
+      <c r="B38" s="4"/>
+      <c r="C38" s="4"/>
+      <c r="D38" s="4"/>
+      <c r="E38" s="4"/>
+      <c r="F38" s="4"/>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+      <c r="I38" s="4"/>
+      <c r="J38" s="4"/>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A39" s="4"/>
+      <c r="B39" s="4"/>
+      <c r="C39" s="4"/>
+      <c r="D39" s="4"/>
+      <c r="E39" s="4"/>
+      <c r="F39" s="4"/>
+      <c r="G39" s="4"/>
+      <c r="H39" s="4"/>
+      <c r="I39" s="4"/>
+      <c r="J39" s="4"/>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A40" s="4"/>
+      <c r="B40" s="4"/>
+      <c r="C40" s="4"/>
+      <c r="D40" s="4"/>
+      <c r="E40" s="4"/>
+      <c r="F40" s="4"/>
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
+      <c r="I40" s="4"/>
+      <c r="J40" s="4"/>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A41" s="4"/>
+      <c r="B41" s="4"/>
+      <c r="C41" s="4"/>
+      <c r="D41" s="4"/>
+      <c r="E41" s="4"/>
+      <c r="F41" s="4"/>
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
+      <c r="I41" s="4"/>
+      <c r="J41" s="4"/>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A42" s="4"/>
+      <c r="B42" s="4"/>
+      <c r="C42" s="4"/>
+      <c r="D42" s="4"/>
+      <c r="E42" s="4"/>
+      <c r="F42" s="4"/>
+      <c r="G42" s="4"/>
+      <c r="H42" s="4"/>
+      <c r="I42" s="4"/>
+      <c r="J42" s="4"/>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A43" s="4"/>
+      <c r="B43" s="4"/>
+      <c r="C43" s="4"/>
+      <c r="D43" s="4"/>
+      <c r="E43" s="4"/>
+      <c r="F43" s="4"/>
+      <c r="G43" s="4"/>
+      <c r="H43" s="4"/>
+      <c r="I43" s="4"/>
+      <c r="J43" s="4"/>
+    </row>
+  </sheetData>
+  <mergeCells count="104">
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="F28:H28"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="F26:H26"/>
+    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="I27:J27"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="F24:H24"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="F25:H25"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="F22:H22"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="F20:H20"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="F21:H21"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="F18:H18"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="F16:H16"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="F15:H15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="G8:J8"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="G9:J9"/>
+    <mergeCell ref="B11:J11"/>
+    <mergeCell ref="B12:J12"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="G5:J5"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="G6:J6"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="G7:J7"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="F1:J1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
 </file>